--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Human Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB79B57B-F75C-4797-BBEB-F8D398CBC95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -38,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,30 +77,26 @@
     <t>contents10</t>
   </si>
   <si>
-    <t>안녕하세얌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>꺼져</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄹㅇㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>야르</t>
+    <t>printType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inoder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delaytime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -490,90 +476,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.69921875" style="1"/>
-    <col min="3" max="3" width="9.296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="1"/>
+    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.8984375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.19921875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.296875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.69921875" style="1"/>
+    <col min="6" max="6" width="10.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.4140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.9140625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.58203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.25" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
